--- a/欣瑞达屏幕通信协议(已自动还原)SVN.xlsx
+++ b/欣瑞达屏幕通信协议(已自动还原)SVN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SVN_WORKSPACE\XRD_shengmeiUI\XRD_shengmeiUI_V2.0.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5C237E-3FC5-4012-BE79-1B15E9BC263D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA3DACCD-5EC0-43D5-AD8B-DA9EE42A0D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-30" windowWidth="22620" windowHeight="13500" xr2:uid="{58889F16-31E8-452B-B49F-853BD7F2930C}"/>
+    <workbookView xWindow="360" yWindow="760" windowWidth="22040" windowHeight="12920" xr2:uid="{58889F16-31E8-452B-B49F-853BD7F2930C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2204,30 +2204,6 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2237,6 +2213,30 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2575,15 +2575,15 @@
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="70" t="s">
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="71"/>
+      <c r="G1" s="77"/>
       <c r="H1" s="5" t="s">
         <v>226</v>
       </c>
@@ -2608,12 +2608,12 @@
       <c r="O1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="68" t="s">
+      <c r="P1" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
-      <c r="S1" s="68"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -2625,14 +2625,14 @@
       <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="D2" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="70" t="s">
+      <c r="E2" s="77"/>
+      <c r="F2" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="71"/>
+      <c r="G2" s="77"/>
       <c r="H2" s="5" t="s">
         <v>6</v>
       </c>
@@ -2678,14 +2678,14 @@
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="D3" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="71"/>
-      <c r="F3" s="70" t="s">
+      <c r="E3" s="77"/>
+      <c r="F3" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="71"/>
+      <c r="G3" s="77"/>
       <c r="H3" s="5" t="s">
         <v>6</v>
       </c>
@@ -2726,15 +2726,15 @@
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
-      <c r="C4" s="69" t="s">
+      <c r="C4" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="72" t="s">
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="73"/>
+      <c r="G4" s="75"/>
       <c r="H4" s="14" t="s">
         <v>226</v>
       </c>
@@ -2744,12 +2744,12 @@
       <c r="J4" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="K4" s="69" t="s">
+      <c r="K4" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="79"/>
       <c r="O4" s="14"/>
       <c r="P4" s="14"/>
       <c r="Q4" s="14"/>
@@ -2766,14 +2766,14 @@
       <c r="C5" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="72" t="s">
+      <c r="D5" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="73"/>
-      <c r="F5" s="72" t="s">
+      <c r="E5" s="75"/>
+      <c r="F5" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="73"/>
+      <c r="G5" s="75"/>
       <c r="H5" s="14" t="s">
         <v>6</v>
       </c>
@@ -2809,14 +2809,14 @@
       <c r="C6" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="72" t="s">
+      <c r="D6" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="73"/>
-      <c r="F6" s="72" t="s">
+      <c r="E6" s="75"/>
+      <c r="F6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="73"/>
+      <c r="G6" s="75"/>
       <c r="H6" s="14" t="s">
         <v>6</v>
       </c>
@@ -2873,7 +2873,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="75">
+      <c r="A12" s="73">
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -2900,7 +2900,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" s="49" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="75"/>
+      <c r="A13" s="73"/>
       <c r="B13" s="43" t="s">
         <v>18</v>
       </c>
@@ -2938,7 +2938,7 @@
       <c r="V13" s="48"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="75"/>
+      <c r="A14" s="73"/>
       <c r="B14" s="2" t="s">
         <v>20</v>
       </c>
@@ -2963,7 +2963,7 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="75"/>
+      <c r="A15" s="73"/>
       <c r="B15" s="2" t="s">
         <v>52</v>
       </c>
@@ -2988,7 +2988,7 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="75"/>
+      <c r="A16" s="73"/>
       <c r="B16" s="9" t="s">
         <v>243</v>
       </c>
@@ -3013,7 +3013,7 @@
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A17" s="75"/>
+      <c r="A17" s="73"/>
       <c r="B17" s="2" t="s">
         <v>50</v>
       </c>
@@ -3038,7 +3038,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A18" s="75"/>
+      <c r="A18" s="73"/>
       <c r="B18" s="2" t="s">
         <v>51</v>
       </c>
@@ -3063,7 +3063,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A19" s="75"/>
+      <c r="A19" s="73"/>
       <c r="B19" s="27" t="s">
         <v>347</v>
       </c>
@@ -3088,7 +3088,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" s="41" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="75"/>
+      <c r="A20" s="73"/>
       <c r="B20" s="2" t="s">
         <v>33</v>
       </c>
@@ -3188,7 +3188,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A23" s="75">
+      <c r="A23" s="73">
         <v>3</v>
       </c>
       <c r="B23" s="17" t="s">
@@ -3215,7 +3215,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A24" s="75"/>
+      <c r="A24" s="73"/>
       <c r="B24" s="17" t="s">
         <v>197</v>
       </c>
@@ -3240,7 +3240,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A25" s="75"/>
+      <c r="A25" s="73"/>
       <c r="B25" s="17" t="s">
         <v>54</v>
       </c>
@@ -3265,7 +3265,7 @@
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A26" s="75"/>
+      <c r="A26" s="73"/>
       <c r="B26" s="2" t="s">
         <v>53</v>
       </c>
@@ -3290,7 +3290,7 @@
       </c>
     </row>
     <row r="27" spans="1:22" s="51" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="75"/>
+      <c r="A27" s="73"/>
       <c r="B27" s="53" t="s">
         <v>383</v>
       </c>
@@ -3328,7 +3328,7 @@
       <c r="V27" s="30"/>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A28" s="75">
+      <c r="A28" s="73">
         <v>5</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -3355,7 +3355,7 @@
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A29" s="75"/>
+      <c r="A29" s="73"/>
       <c r="B29" s="32" t="s">
         <v>38</v>
       </c>
@@ -3380,7 +3380,7 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A30" s="75"/>
+      <c r="A30" s="73"/>
       <c r="B30" s="2" t="s">
         <v>39</v>
       </c>
@@ -3405,7 +3405,7 @@
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A31" s="75"/>
+      <c r="A31" s="73"/>
       <c r="B31" s="3" t="s">
         <v>41</v>
       </c>
@@ -3430,7 +3430,7 @@
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A32" s="75"/>
+      <c r="A32" s="73"/>
       <c r="B32" s="2" t="s">
         <v>43</v>
       </c>
@@ -3455,7 +3455,7 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="75"/>
+      <c r="A33" s="73"/>
       <c r="B33" s="17" t="s">
         <v>276</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>4</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I74" s="1">
         <v>1</v>
@@ -4803,10 +4803,10 @@
     </row>
     <row r="88" spans="1:22" s="51" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="30"/>
-      <c r="B88" s="78" t="s">
+      <c r="B88" s="70" t="s">
         <v>436</v>
       </c>
-      <c r="C88" s="79" t="s">
+      <c r="C88" s="71" t="s">
         <v>435</v>
       </c>
       <c r="D88" s="60"/>
@@ -4841,7 +4841,7 @@
       <c r="B89" s="24" t="s">
         <v>342</v>
       </c>
-      <c r="C89" s="77" t="s">
+      <c r="C89" s="69" t="s">
         <v>343</v>
       </c>
       <c r="D89" s="20"/>
@@ -6167,7 +6167,7 @@
       <c r="H137" s="58" t="s">
         <v>393</v>
       </c>
-      <c r="I137" s="74" t="s">
+      <c r="I137" s="72" t="s">
         <v>405</v>
       </c>
       <c r="J137" s="30"/>
@@ -6205,7 +6205,7 @@
       <c r="H138" s="58" t="s">
         <v>396</v>
       </c>
-      <c r="I138" s="74"/>
+      <c r="I138" s="72"/>
       <c r="J138" s="30"/>
       <c r="K138" s="30"/>
       <c r="L138" s="30"/>
@@ -6241,7 +6241,7 @@
       <c r="H139" s="58" t="s">
         <v>408</v>
       </c>
-      <c r="I139" s="74"/>
+      <c r="I139" s="72"/>
       <c r="J139" s="30"/>
       <c r="K139" s="30"/>
       <c r="L139" s="30"/>
@@ -6277,7 +6277,7 @@
       <c r="H140" s="58" t="s">
         <v>409</v>
       </c>
-      <c r="I140" s="74"/>
+      <c r="I140" s="72"/>
       <c r="J140" s="30"/>
       <c r="K140" s="30"/>
       <c r="L140" s="30"/>
@@ -6313,7 +6313,7 @@
       <c r="H141" s="58" t="s">
         <v>400</v>
       </c>
-      <c r="I141" s="74" t="s">
+      <c r="I141" s="72" t="s">
         <v>410</v>
       </c>
       <c r="J141" s="30"/>
@@ -6351,7 +6351,7 @@
       <c r="H142" s="58" t="s">
         <v>402</v>
       </c>
-      <c r="I142" s="74"/>
+      <c r="I142" s="72"/>
       <c r="J142" s="30"/>
       <c r="K142" s="30"/>
       <c r="L142" s="30"/>
@@ -6387,7 +6387,7 @@
       <c r="H143" s="58" t="s">
         <v>406</v>
       </c>
-      <c r="I143" s="74"/>
+      <c r="I143" s="72"/>
       <c r="J143" s="30"/>
       <c r="K143" s="30"/>
       <c r="L143" s="30"/>
@@ -6423,7 +6423,7 @@
       <c r="H144" s="58" t="s">
         <v>407</v>
       </c>
-      <c r="I144" s="74"/>
+      <c r="I144" s="72"/>
       <c r="J144" s="30"/>
       <c r="K144" s="30"/>
       <c r="L144" s="30"/>
@@ -8041,7 +8041,7 @@
         <v>434</v>
       </c>
       <c r="C211" s="54"/>
-      <c r="D211" s="76" t="s">
+      <c r="D211" s="68" t="s">
         <v>433</v>
       </c>
       <c r="E211" s="14" t="s">
@@ -8062,16 +8062,6 @@
     <sortCondition ref="E12:E176"/>
   </sortState>
   <mergeCells count="19">
-    <mergeCell ref="I141:I144"/>
-    <mergeCell ref="I137:I140"/>
-    <mergeCell ref="A12:A20"/>
-    <mergeCell ref="A23:A27"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F6:G6"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="P1:S1"/>
     <mergeCell ref="C4:E4"/>
@@ -8081,6 +8071,16 @@
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="F4:G4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="I141:I144"/>
+    <mergeCell ref="I137:I140"/>
+    <mergeCell ref="A12:A20"/>
+    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="A28:A33"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
